--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525498</v>
+        <v>128525961</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R2" t="n">
-        <v>6425534</v>
+        <v>6425540</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -774,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>91472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -814,13 +817,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,52 +886,49 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525706</v>
+        <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>91472</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567708</v>
+        <v>567763</v>
       </c>
       <c r="R4" t="n">
-        <v>6425486</v>
+        <v>6425534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525392</v>
+        <v>128525972</v>
       </c>
       <c r="B5" t="n">
-        <v>105609</v>
+        <v>58055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,31 +1010,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567703</v>
+        <v>567739</v>
       </c>
       <c r="R5" t="n">
-        <v>6425552</v>
+        <v>6425540</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>105609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,31 +1224,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R7" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Stenberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Björn Stenberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R2" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>91472</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
+        <v>105621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,31 +1010,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R5" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,44 +1105,40 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>58059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1151,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R6" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,49 +1203,53 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525392</v>
+        <v>128525549</v>
       </c>
       <c r="B7" t="n">
-        <v>105609</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567703</v>
+        <v>567747</v>
       </c>
       <c r="R7" t="n">
-        <v>6425552</v>
+        <v>6425516</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128525207</v>
       </c>
       <c r="B10" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128525678</v>
       </c>
       <c r="B11" t="n">
-        <v>57843</v>
+        <v>57847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128525446</v>
       </c>
       <c r="B12" t="n">
-        <v>57698</v>
+        <v>57702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>128525249</v>
       </c>
       <c r="B13" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128525170</v>
+        <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>86944</v>
+        <v>91478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3739</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567802</v>
+        <v>567715</v>
       </c>
       <c r="R14" t="n">
-        <v>6425552</v>
+        <v>6425485</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525814</v>
+        <v>128525170</v>
       </c>
       <c r="B15" t="n">
-        <v>91472</v>
+        <v>86948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>3739</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567715</v>
+        <v>567802</v>
       </c>
       <c r="R15" t="n">
-        <v>6425485</v>
+        <v>6425552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
         <v>128525223</v>
       </c>
       <c r="B16" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128525967</v>
       </c>
       <c r="B17" t="n">
-        <v>57679</v>
+        <v>57683</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128525296</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>128525946</v>
       </c>
       <c r="B20" t="n">
-        <v>91450</v>
+        <v>91456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B2" t="n">
-        <v>91478</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,12 +708,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R2" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,53 +777,49 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525498</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,49 +883,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525498</v>
+        <v>128525706</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>91484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567763</v>
+        <v>567708</v>
       </c>
       <c r="R4" t="n">
-        <v>6425534</v>
+        <v>6425486</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
         <v>128525392</v>
       </c>
       <c r="B5" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,40 +1105,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525972</v>
+        <v>128525549</v>
       </c>
       <c r="B6" t="n">
-        <v>58059</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1148,13 +1152,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567739</v>
+        <v>567747</v>
       </c>
       <c r="R6" t="n">
-        <v>6425540</v>
+        <v>6425516</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,51 +1207,47 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>58059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R7" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128525814</v>
+        <v>128525170</v>
       </c>
       <c r="B14" t="n">
-        <v>91478</v>
+        <v>86954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>3739</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567715</v>
+        <v>567802</v>
       </c>
       <c r="R14" t="n">
-        <v>6425485</v>
+        <v>6425552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525170</v>
+        <v>128525814</v>
       </c>
       <c r="B15" t="n">
-        <v>86948</v>
+        <v>91484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3739</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567802</v>
+        <v>567715</v>
       </c>
       <c r="R15" t="n">
-        <v>6425552</v>
+        <v>6425485</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
         <v>128525223</v>
       </c>
       <c r="B16" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>128525946</v>
       </c>
       <c r="B20" t="n">
-        <v>91456</v>
+        <v>91462</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525961</v>
+        <v>128525498</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R2" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,49 +774,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525498</v>
+        <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>91486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567763</v>
+        <v>567708</v>
       </c>
       <c r="R3" t="n">
-        <v>6425534</v>
+        <v>6425486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B4" t="n">
-        <v>91484</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -923,12 +923,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R4" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +981,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,49 +992,53 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525392</v>
+        <v>128525549</v>
       </c>
       <c r="B5" t="n">
-        <v>105630</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567703</v>
+        <v>567747</v>
       </c>
       <c r="R5" t="n">
-        <v>6425552</v>
+        <v>6425516</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1090,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,51 +1101,47 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>58059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1152,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R6" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,17 +1206,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>58059</v>
+        <v>105642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,31 +1224,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R7" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128525170</v>
+        <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>86954</v>
+        <v>91486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3739</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567802</v>
+        <v>567715</v>
       </c>
       <c r="R14" t="n">
-        <v>6425552</v>
+        <v>6425485</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525814</v>
+        <v>128525170</v>
       </c>
       <c r="B15" t="n">
-        <v>91484</v>
+        <v>86956</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>3739</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567715</v>
+        <v>567802</v>
       </c>
       <c r="R15" t="n">
-        <v>6425485</v>
+        <v>6425552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
         <v>128525223</v>
       </c>
       <c r="B16" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Björn Stenberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>128525946</v>
       </c>
       <c r="B20" t="n">
-        <v>91462</v>
+        <v>91464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Björn Stenberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525498</v>
+        <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>91486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567763</v>
+        <v>567708</v>
       </c>
       <c r="R2" t="n">
-        <v>6425534</v>
+        <v>6425486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>91486</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -814,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,53 +886,49 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525961</v>
+        <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R4" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,6 +980,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Stenberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Björn Stenberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,45 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525706</v>
+        <v>128525498</v>
       </c>
       <c r="B2" t="n">
-        <v>91486</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567708</v>
+        <v>567763</v>
       </c>
       <c r="R2" t="n">
-        <v>6425486</v>
+        <v>6425534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>91486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,13 +814,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,49 +883,53 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525498</v>
+        <v>128525961</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R4" t="n">
-        <v>6425534</v>
+        <v>6425540</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +981,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525498</v>
+        <v>128525961</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R2" t="n">
-        <v>6425534</v>
+        <v>6425540</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +787,7 @@
         <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,46 +893,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525961</v>
+        <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R4" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,6 +980,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128525814</v>
+        <v>128525170</v>
       </c>
       <c r="B14" t="n">
-        <v>91486</v>
+        <v>86956</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>3739</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567715</v>
+        <v>567802</v>
       </c>
       <c r="R14" t="n">
-        <v>6425485</v>
+        <v>6425552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525170</v>
+        <v>128525814</v>
       </c>
       <c r="B15" t="n">
-        <v>86956</v>
+        <v>91487</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3739</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567802</v>
+        <v>567715</v>
       </c>
       <c r="R15" t="n">
-        <v>6425552</v>
+        <v>6425485</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
         <v>128525223</v>
       </c>
       <c r="B16" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Björn Stenberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>128525946</v>
       </c>
       <c r="B20" t="n">
-        <v>91464</v>
+        <v>91465</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R2" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>91487</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,44 +999,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>58086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1046,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R5" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,47 +1097,51 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525972</v>
+        <v>128525549</v>
       </c>
       <c r="B6" t="n">
-        <v>58059</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567739</v>
+        <v>567747</v>
       </c>
       <c r="R6" t="n">
-        <v>6425540</v>
+        <v>6425516</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128525207</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128525678</v>
       </c>
       <c r="B11" t="n">
-        <v>57847</v>
+        <v>57874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128525446</v>
       </c>
       <c r="B12" t="n">
-        <v>57702</v>
+        <v>57729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>128525249</v>
       </c>
       <c r="B13" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128525170</v>
       </c>
       <c r="B14" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128525814</v>
       </c>
       <c r="B15" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128525223</v>
       </c>
       <c r="B16" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128525967</v>
       </c>
       <c r="B17" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128525296</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>128525946</v>
       </c>
       <c r="B20" t="n">
-        <v>91465</v>
+        <v>91492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,12 +708,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R2" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>91519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,13 +817,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128525170</v>
+        <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>86983</v>
+        <v>91519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3739</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567802</v>
+        <v>567715</v>
       </c>
       <c r="R14" t="n">
-        <v>6425552</v>
+        <v>6425485</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525814</v>
+        <v>128525170</v>
       </c>
       <c r="B15" t="n">
-        <v>91514</v>
+        <v>86987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>3739</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567715</v>
+        <v>567802</v>
       </c>
       <c r="R15" t="n">
-        <v>6425485</v>
+        <v>6425552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
         <v>128525223</v>
       </c>
       <c r="B16" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Stenberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
         <v>128525412</v>
       </c>
       <c r="B18" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>128525946</v>
       </c>
       <c r="B20" t="n">
-        <v>91492</v>
+        <v>91497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R2" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>91519</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,40 +999,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525972</v>
+        <v>128525549</v>
       </c>
       <c r="B5" t="n">
-        <v>58086</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1042,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567739</v>
+        <v>567747</v>
       </c>
       <c r="R5" t="n">
-        <v>6425540</v>
+        <v>6425516</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,51 +1101,47 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>58086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R6" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525170</v>
+        <v>128525223</v>
       </c>
       <c r="B15" t="n">
-        <v>86987</v>
+        <v>92136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3739</v>
+        <v>6031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567802</v>
+        <v>567759</v>
       </c>
       <c r="R15" t="n">
-        <v>6425552</v>
+        <v>6425594</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128525223</v>
+        <v>128525967</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>57710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6031</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2226,12 +2226,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2239,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567759</v>
+        <v>567739</v>
       </c>
       <c r="R16" t="n">
-        <v>6425594</v>
+        <v>6425540</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2283,7 +2284,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128525967</v>
+        <v>128525412</v>
       </c>
       <c r="B17" t="n">
-        <v>57710</v>
+        <v>105695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,35 +2313,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2349,13 +2345,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567739</v>
+        <v>567760</v>
       </c>
       <c r="R17" t="n">
-        <v>6425540</v>
+        <v>6425550</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,6 +2389,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2404,49 +2401,53 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128525412</v>
+        <v>128525296</v>
       </c>
       <c r="B18" t="n">
-        <v>105688</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567760</v>
+        <v>567734</v>
       </c>
       <c r="R18" t="n">
-        <v>6425550</v>
+        <v>6425606</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,13 +2493,17 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2517,46 +2522,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128525296</v>
+        <v>128525946</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>91502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1110</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2564,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567734</v>
+        <v>567714</v>
       </c>
       <c r="R19" t="n">
-        <v>6425606</v>
+        <v>6425492</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2608,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bearbetat torrträd</t>
+          <t>På tallstubbe omgiven av gamla och mkt grova tallar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,6 +2617,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,44 +2629,44 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128525946</v>
+        <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>91497</v>
+        <v>86988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1110</v>
+        <v>3739</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567714</v>
+        <v>567802</v>
       </c>
       <c r="R20" t="n">
-        <v>6425492</v>
+        <v>6425552</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,11 +2720,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tallstubbe omgiven av gamla och mkt grova tallar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -999,46 +999,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525549</v>
+        <v>128525392</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>105695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567747</v>
+        <v>567703</v>
       </c>
       <c r="R5" t="n">
-        <v>6425516</v>
+        <v>6425552</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,7 +1098,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1213,42 +1210,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525392</v>
+        <v>128525549</v>
       </c>
       <c r="B7" t="n">
-        <v>105695</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567703</v>
+        <v>567747</v>
       </c>
       <c r="R7" t="n">
-        <v>6425552</v>
+        <v>6425516</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -999,42 +999,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525392</v>
+        <v>128525549</v>
       </c>
       <c r="B5" t="n">
-        <v>105695</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567703</v>
+        <v>567747</v>
       </c>
       <c r="R5" t="n">
-        <v>6425552</v>
+        <v>6425516</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1090,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,17 +1101,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B6" t="n">
-        <v>58086</v>
+        <v>105695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,31 +1119,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R6" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,44 +1214,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>58086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R7" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,44 +999,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525549</v>
+        <v>128525972</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>58090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1046,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567747</v>
+        <v>567739</v>
       </c>
       <c r="R5" t="n">
-        <v>6425516</v>
+        <v>6425540</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,49 +1097,53 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525392</v>
+        <v>128525549</v>
       </c>
       <c r="B6" t="n">
-        <v>105695</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567703</v>
+        <v>567747</v>
       </c>
       <c r="R6" t="n">
-        <v>6425552</v>
+        <v>6425516</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1207,17 +1206,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>58086</v>
+        <v>105699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,31 +1224,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R7" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128525207</v>
       </c>
       <c r="B10" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128525678</v>
       </c>
       <c r="B11" t="n">
-        <v>57874</v>
+        <v>57878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128525446</v>
       </c>
       <c r="B12" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>128525249</v>
       </c>
       <c r="B13" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128525223</v>
       </c>
       <c r="B15" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128525967</v>
       </c>
       <c r="B16" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128525412</v>
       </c>
       <c r="B17" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>128525296</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>128525946</v>
       </c>
       <c r="B19" t="n">
-        <v>91502</v>
+        <v>91506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,45 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525706</v>
+        <v>128525498</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567708</v>
+        <v>567763</v>
       </c>
       <c r="R2" t="n">
-        <v>6425486</v>
+        <v>6425534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>91528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,13 +814,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,49 +883,53 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525498</v>
+        <v>128525961</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R4" t="n">
-        <v>6425534</v>
+        <v>6425540</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +981,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,47 +992,51 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525972</v>
+        <v>128525549</v>
       </c>
       <c r="B5" t="n">
-        <v>58090</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1042,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567739</v>
+        <v>567747</v>
       </c>
       <c r="R5" t="n">
-        <v>6425540</v>
+        <v>6425516</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,53 +1101,49 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525549</v>
+        <v>128525392</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>105699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567747</v>
+        <v>567703</v>
       </c>
       <c r="R6" t="n">
-        <v>6425516</v>
+        <v>6425552</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,17 +1207,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525392</v>
+        <v>128525972</v>
       </c>
       <c r="B7" t="n">
-        <v>105699</v>
+        <v>58090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,31 +1225,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567703</v>
+        <v>567739</v>
       </c>
       <c r="R7" t="n">
-        <v>6425552</v>
+        <v>6425540</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525498</v>
+        <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567763</v>
+        <v>567708</v>
       </c>
       <c r="R2" t="n">
-        <v>6425534</v>
+        <v>6425486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>91528</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -814,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,53 +886,49 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525961</v>
+        <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R4" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,6 +980,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,46 +784,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525498</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,49 +883,53 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525498</v>
+        <v>128525961</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R4" t="n">
-        <v>6425534</v>
+        <v>6425540</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +981,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
         <v>128525549</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525392</v>
+        <v>128525972</v>
       </c>
       <c r="B6" t="n">
-        <v>105699</v>
+        <v>58093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567703</v>
+        <v>567739</v>
       </c>
       <c r="R6" t="n">
-        <v>6425552</v>
+        <v>6425540</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>58090</v>
+        <v>105706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,31 +1224,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R7" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128525207</v>
       </c>
       <c r="B10" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128525678</v>
       </c>
       <c r="B11" t="n">
-        <v>57878</v>
+        <v>57881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128525446</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>128525249</v>
       </c>
       <c r="B13" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128525223</v>
       </c>
       <c r="B15" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128525967</v>
       </c>
       <c r="B16" t="n">
-        <v>57714</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128525412</v>
       </c>
       <c r="B17" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>128525296</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>128525946</v>
       </c>
       <c r="B19" t="n">
-        <v>91506</v>
+        <v>91511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R2" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525961</v>
       </c>
       <c r="B3" t="n">
-        <v>91535</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567739</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>128525498</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525392</v>
+        <v>128525972</v>
       </c>
       <c r="B6" t="n">
-        <v>105709</v>
+        <v>58093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567703</v>
+        <v>567739</v>
       </c>
       <c r="R6" t="n">
-        <v>6425552</v>
+        <v>6425540</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525972</v>
+        <v>128525392</v>
       </c>
       <c r="B7" t="n">
-        <v>58093</v>
+        <v>105714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,31 +1224,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567739</v>
+        <v>567703</v>
       </c>
       <c r="R7" t="n">
-        <v>6425540</v>
+        <v>6425552</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128525492</v>
       </c>
       <c r="B8" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128525536</v>
       </c>
       <c r="B9" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128525814</v>
       </c>
       <c r="B14" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128525223</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128525412</v>
       </c>
       <c r="B17" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>128525946</v>
       </c>
       <c r="B19" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,45 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525706</v>
+        <v>128525498</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567708</v>
+        <v>567763</v>
       </c>
       <c r="R2" t="n">
-        <v>6425486</v>
+        <v>6425534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525961</v>
+        <v>128525706</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,13 +814,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567739</v>
+        <v>567708</v>
       </c>
       <c r="R3" t="n">
-        <v>6425540</v>
+        <v>6425486</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,49 +883,53 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525498</v>
+        <v>128525961</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R4" t="n">
-        <v>6425534</v>
+        <v>6425540</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +981,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,53 +992,49 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525549</v>
+        <v>128525392</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>105714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567747</v>
+        <v>567703</v>
       </c>
       <c r="R5" t="n">
-        <v>6425516</v>
+        <v>6425552</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,7 +1098,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1213,42 +1210,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525392</v>
+        <v>128525549</v>
       </c>
       <c r="B7" t="n">
-        <v>105714</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567703</v>
+        <v>567747</v>
       </c>
       <c r="R7" t="n">
-        <v>6425552</v>
+        <v>6425516</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2525,7 +2525,7 @@
         <v>128525946</v>
       </c>
       <c r="B19" t="n">
-        <v>91518</v>
+        <v>91524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87014</v>
+        <v>87021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87023</v>
+        <v>87024</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>128525170</v>
       </c>
       <c r="B20" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37525-2025 artfynd.xlsx
+++ b/artfynd/A 37525-2025 artfynd.xlsx
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128525498</v>
+        <v>128525946</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>91907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567763</v>
+        <v>567714</v>
       </c>
       <c r="R2" t="n">
-        <v>6425534</v>
+        <v>6425492</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tallstubbe omgiven av gamla och mkt grova tallar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128525706</v>
+        <v>128525170</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>3739</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567708</v>
+        <v>567802</v>
       </c>
       <c r="R3" t="n">
-        <v>6425486</v>
+        <v>6425552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,17 +891,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128525961</v>
+        <v>128525492</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -923,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567739</v>
+        <v>567763</v>
       </c>
       <c r="R4" t="n">
-        <v>6425540</v>
+        <v>6425534</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,49 +1000,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128525392</v>
+        <v>128525706</v>
       </c>
       <c r="B5" t="n">
-        <v>105714</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567703</v>
+        <v>567708</v>
       </c>
       <c r="R5" t="n">
-        <v>6425552</v>
+        <v>6425486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,49 +1109,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128525972</v>
+        <v>128525814</v>
       </c>
       <c r="B6" t="n">
-        <v>58093</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567739</v>
+        <v>567715</v>
       </c>
       <c r="R6" t="n">
-        <v>6425540</v>
+        <v>6425485</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,6 +1206,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,39 +1218,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128525549</v>
+        <v>128525223</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>92567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,13 +1258,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567747</v>
+        <v>567759</v>
       </c>
       <c r="R7" t="n">
-        <v>6425516</v>
+        <v>6425594</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1315,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,17 +1327,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128525492</v>
+        <v>128525446</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>57966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1352,12 +1367,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1384,10 @@
         <v>567763</v>
       </c>
       <c r="R8" t="n">
-        <v>6425534</v>
+        <v>6425545</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,7 +1425,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,17 +1436,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128525536</v>
+        <v>128525296</v>
       </c>
       <c r="B9" t="n">
-        <v>105714</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,31 +1454,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567766</v>
+        <v>567734</v>
       </c>
       <c r="R9" t="n">
-        <v>6425517</v>
+        <v>6425606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,13 +1528,17 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,39 +1550,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128525207</v>
+        <v>128525961</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1571,7 +1594,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1581,13 +1604,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567794</v>
+        <v>567739</v>
       </c>
       <c r="R10" t="n">
-        <v>6425555</v>
+        <v>6425540</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,32 +1666,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128525678</v>
+        <v>128525249</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1680,7 +1703,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1690,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567693</v>
+        <v>567759</v>
       </c>
       <c r="R11" t="n">
-        <v>6425492</v>
+        <v>6425594</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,6 +1749,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,39 +1773,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128525446</v>
+        <v>128525967</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567763</v>
+        <v>567739</v>
       </c>
       <c r="R12" t="n">
-        <v>6425545</v>
+        <v>6425540</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1854,17 +1882,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128525249</v>
+        <v>128525972</v>
       </c>
       <c r="B13" t="n">
-        <v>56913</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,33 +1900,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1908,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567759</v>
+        <v>567739</v>
       </c>
       <c r="R13" t="n">
-        <v>6425594</v>
+        <v>6425540</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1944,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128525814</v>
+        <v>128525678</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>58112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +2005,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>103020</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2008,12 +2027,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,13 +2041,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567715</v>
+        <v>567693</v>
       </c>
       <c r="R14" t="n">
-        <v>6425485</v>
+        <v>6425492</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2065,7 +2085,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2084,32 +2103,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128525223</v>
+        <v>128525207</v>
       </c>
       <c r="B15" t="n">
-        <v>92153</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2117,12 +2136,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2130,13 +2150,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567759</v>
+        <v>567794</v>
       </c>
       <c r="R15" t="n">
-        <v>6425594</v>
+        <v>6425555</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,7 +2194,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2193,32 +2212,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128525967</v>
+        <v>128525549</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2230,7 +2249,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2240,13 +2259,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567739</v>
+        <v>567747</v>
       </c>
       <c r="R16" t="n">
-        <v>6425540</v>
+        <v>6425516</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2302,32 +2321,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128525412</v>
+        <v>128525498</v>
       </c>
       <c r="B17" t="n">
-        <v>105714</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567760</v>
+        <v>567763</v>
       </c>
       <c r="R17" t="n">
-        <v>6425550</v>
+        <v>6425534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,53 +2420,49 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128525296</v>
+        <v>128525392</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>106244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2455,10 +2470,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567734</v>
+        <v>567703</v>
       </c>
       <c r="R18" t="n">
-        <v>6425606</v>
+        <v>6425552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,17 +2508,13 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2522,45 +2533,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128525946</v>
+        <v>128525412</v>
       </c>
       <c r="B19" t="n">
-        <v>91524</v>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1110</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2568,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567714</v>
+        <v>567760</v>
       </c>
       <c r="R19" t="n">
-        <v>6425492</v>
+        <v>6425550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,11 +2614,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstubbe omgiven av gamla och mkt grova tallar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2629,52 +2632,49 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128525170</v>
+        <v>128525536</v>
       </c>
       <c r="B20" t="n">
-        <v>87029</v>
+        <v>106244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3739</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567802</v>
+        <v>567766</v>
       </c>
       <c r="R20" t="n">
-        <v>6425552</v>
+        <v>6425517</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
